--- a/ig-news/plan/hotcoin-content-calendar.xlsx
+++ b/ig-news/plan/hotcoin-content-calendar.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
-          <t>WHAT IF: Xbox 360 ($399, 2005) or $399 in Microsoft? Dot = console</t>
+          <t>WHAT IF: Xbox 360 ($399, 2005) or $399 in Microsoft? -&gt; $7,591 (scheduled, real photo dot)</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">

--- a/ig-news/plan/hotcoin-content-calendar.xlsx
+++ b/ig-news/plan/hotcoin-content-calendar.xlsx
@@ -767,12 +767,12 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>Live pick. Ready angle: Amazon + Strategy results</t>
+          <t>Suspected $5.5B Binance hack (scheduled; developing story, re-check at 15:40)</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Myth vs Fact: "Sell in May, buy at Halloween". Tested on 30 years of S&amp;P data</t>
+          <t>Myth vs Fact: "Sell in May" would have halved your gains (scheduled)</t>
         </is>
       </c>
       <c r="G7" s="27" t="inlineStr">

--- a/ig-news/plan/hotcoin-content-calendar.xlsx
+++ b/ig-news/plan/hotcoin-content-calendar.xlsx
@@ -767,7 +767,7 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>Suspected $5.5B Binance hack (scheduled; developing story, re-check at 15:40)</t>
+          <t>BREAKING (published 09:04 on owner request): $5.7B Binance hack, carousel + paper-desk explainer Reel on IG, FB, TikTok, LinkedIn (not X)</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">

--- a/ig-news/plan/hotcoin-content-calendar.xlsx
+++ b/ig-news/plan/hotcoin-content-calendar.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="G7" s="27" t="inlineStr">
         <is>
-          <t>WHAT IF: Amazon Prime ($79, 2005) or $79 in Amazon? Dot = parcel box</t>
+          <t>WHAT IF: Amazon Prime ($79, 2005) or $79 in Amazon? -&gt; $9,197 (scheduled, payoff hook on frame 1)</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">

--- a/ig-news/plan/hotcoin-content-calendar.xlsx
+++ b/ig-news/plan/hotcoin-content-calendar.xlsx
@@ -807,12 +807,12 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>Live pick. Fallback: Bitcoin whitepaper, 18 years (Oct 31, 2008)</t>
+          <t>Binance hack update: $6.3B, investigators point to North Korea (scheduled, Teng face cover)</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Crypto 101: the 9-page whitepaper that started Bitcoin (timeline)</t>
+          <t>Crypto 101 ON THIS DAY: whitepaper turns 18, 9 pages -&gt; $1.5T (scheduled)</t>
         </is>
       </c>
       <c r="G8" s="26" t="inlineStr">

--- a/ig-news/plan/hotcoin-content-calendar.xlsx
+++ b/ig-news/plan/hotcoin-content-calendar.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="G8" s="26" t="inlineStr">
         <is>
-          <t>TIER LIST: scariest crashes ever ranked (1929, 2008, Covid, LUNA, FTX...)</t>
+          <t>TIER LIST: scariest crashes ever ranked (scheduled; S: LUNA, 1929 ... D: Black Monday)</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
